--- a/其它文件/报告模板登记.xlsx
+++ b/其它文件/报告模板登记.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19095" windowHeight="11490"/>
+    <workbookView windowWidth="19035" windowHeight="12105"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="798">
   <si>
     <t>模板名称</t>
   </si>
@@ -45,6 +45,9 @@
   </si>
   <si>
     <t>入口路径</t>
+  </si>
+  <si>
+    <t>同步模板日期</t>
   </si>
   <si>
     <t>ope</t>
@@ -2906,12 +2909,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF7A7E85"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF8C8C8C"/>
@@ -2958,6 +2955,12 @@
       <sz val="12"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF7A7E85"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3190,15 +3193,15 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <i/>
       <sz val="12"/>
       <color rgb="FF080808"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Courier New"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -3700,12 +3703,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -3724,11 +3727,11 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -4088,7 +4091,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N163"/>
+  <dimension ref="A1:O163"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="40.247619047619" style="4" customWidth="1"/>
@@ -4096,14 +4099,14 @@
     <col min="3" max="3" width="15.5047619047619" style="6" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" customWidth="1"/>
     <col min="5" max="5" width="13" style="5" customWidth="1"/>
-    <col min="6" max="6" width="27.3714285714286" style="5" customWidth="1"/>
-    <col min="7" max="7" width="13.8571428571429" style="4" customWidth="1"/>
-    <col min="8" max="8" width="13.752380952381" style="4" customWidth="1"/>
-    <col min="9" max="9" width="19.7142857142857" style="4" customWidth="1"/>
-    <col min="10" max="10" width="28.3714285714286" style="4" customWidth="1"/>
+    <col min="6" max="7" width="27.3714285714286" style="5" customWidth="1"/>
+    <col min="8" max="8" width="13.8571428571429" style="4" customWidth="1"/>
+    <col min="9" max="9" width="13.752380952381" style="4" customWidth="1"/>
+    <col min="10" max="10" width="19.7142857142857" style="4" customWidth="1"/>
+    <col min="11" max="11" width="28.3714285714286" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4122,7 +4125,7 @@
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
@@ -4131,216 +4134,219 @@
       <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="5">
         <v>300011</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="5">
         <v>200007</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="5">
         <v>400037</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="4" t="s">
         <v>17</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="5">
         <v>500003</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="5">
         <v>300010</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="5">
         <v>300013</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" s="5">
         <v>400038</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5">
         <v>300008</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" s="5">
         <v>400046</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:7">
+      <c r="H10" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:8">
       <c r="A11" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:10">
+      <c r="H11" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:11">
       <c r="A12" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J12" s="4" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:7">
+      <c r="K12" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:8">
       <c r="A13" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13" s="4" t="s">
         <v>56</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1" spans="1:6">
       <c r="A15" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B15" s="5">
         <v>390005</v>
@@ -4352,26 +4358,23 @@
         <v>1017</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16" s="5">
         <v>700003</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16" s="4" t="s">
         <v>66</v>
       </c>
       <c r="H16" s="4" t="s">
@@ -4380,2271 +4383,2354 @@
       <c r="I16" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="17" customFormat="1" spans="1:10">
+      <c r="J16" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" spans="1:11">
       <c r="A17" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B17" s="5">
         <v>400045</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G17" s="4"/>
+        <v>74</v>
+      </c>
+      <c r="G17" s="5"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" spans="1:10">
+      <c r="J17" s="4"/>
+      <c r="K17" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" spans="1:11">
       <c r="A18" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B18" s="5">
         <v>400035</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G18" s="4"/>
+        <v>80</v>
+      </c>
+      <c r="G18" s="5"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
-    </row>
-    <row r="19" customFormat="1" spans="1:10">
+      <c r="K18" s="4"/>
+    </row>
+    <row r="19" customFormat="1" spans="1:11">
       <c r="A19" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B19" s="5">
         <v>300012</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G19" s="4"/>
+        <v>85</v>
+      </c>
+      <c r="G19" s="5"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
-    </row>
-    <row r="20" customFormat="1" spans="1:10">
+      <c r="K19" s="4"/>
+    </row>
+    <row r="20" customFormat="1" spans="1:11">
       <c r="A20" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B20" s="5">
         <v>400017</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G20" s="4"/>
+        <v>90</v>
+      </c>
+      <c r="G20" s="5"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
-    </row>
-    <row r="21" customFormat="1" spans="1:10">
+      <c r="K20" s="4"/>
+    </row>
+    <row r="21" customFormat="1" spans="1:11">
       <c r="A21" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B21" s="5">
         <v>400021</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="G21" s="4"/>
+        <v>95</v>
+      </c>
+      <c r="G21" s="5"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="K21" s="4"/>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B22" s="5">
         <v>800007</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="I22" s="21"/>
-    </row>
-    <row r="23" customFormat="1" spans="1:10">
+        <v>99</v>
+      </c>
+      <c r="J22" s="20"/>
+    </row>
+    <row r="23" customFormat="1" spans="1:11">
       <c r="A23" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B23" s="5">
         <v>110005</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F23" s="5"/>
-      <c r="G23" s="4">
+      <c r="G23" s="5"/>
+      <c r="H23" s="4">
         <v>6</v>
       </c>
-      <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
-    </row>
-    <row r="24" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="K23" s="4"/>
+    </row>
+    <row r="24" customFormat="1" ht="18" customHeight="1" spans="1:11">
       <c r="A24" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B24" s="5">
         <v>110010</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F24" s="5"/>
-      <c r="G24" s="4">
+      <c r="G24" s="5"/>
+      <c r="H24" s="4">
         <v>4</v>
       </c>
-      <c r="H24" s="4"/>
       <c r="I24" s="4"/>
-      <c r="J24" s="22"/>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="J24" s="4"/>
+      <c r="K24" s="21"/>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B25" s="5">
         <v>110009</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="G25" s="4">
+        <v>109</v>
+      </c>
+      <c r="H25" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="26" customFormat="1" spans="1:10">
+    <row r="26" customFormat="1" spans="1:11">
       <c r="A26" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B26" s="5">
         <v>110003</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G26" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H26" s="4"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="4" t="s">
+        <v>114</v>
+      </c>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
-    </row>
-    <row r="27" customFormat="1" spans="1:10">
+      <c r="K26" s="4"/>
+    </row>
+    <row r="27" customFormat="1" spans="1:11">
       <c r="A27" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B27" s="5">
         <v>110019</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="G27" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="H27" s="4"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="10" t="s">
+        <v>119</v>
+      </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
-    </row>
-    <row r="28" customFormat="1" spans="1:10">
+      <c r="K27" s="4"/>
+    </row>
+    <row r="28" customFormat="1" spans="1:11">
       <c r="A28" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B28" s="5">
         <v>110020</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F28" s="5"/>
-      <c r="G28" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="H28" s="4"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="4" t="s">
+        <v>123</v>
+      </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
-    </row>
-    <row r="29" customFormat="1" spans="1:10">
+      <c r="K28" s="4"/>
+    </row>
+    <row r="29" customFormat="1" spans="1:11">
       <c r="A29" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B29" s="5">
         <v>110012</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="H29" s="4"/>
+        <v>127</v>
+      </c>
+      <c r="G29" s="5"/>
+      <c r="H29" s="4" t="s">
+        <v>123</v>
+      </c>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
-    </row>
-    <row r="30" customFormat="1" spans="1:10">
+      <c r="K29" s="4"/>
+    </row>
+    <row r="30" customFormat="1" spans="1:11">
       <c r="A30" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B30" s="5">
         <v>110007</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="G30" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4" t="s">
+      <c r="G30" s="5"/>
+      <c r="H30" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="J30" s="4"/>
-    </row>
-    <row r="31" customFormat="1" spans="1:11">
+      <c r="I30" s="4"/>
+      <c r="J30" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="K30" s="4"/>
+    </row>
+    <row r="31" customFormat="1" spans="1:12">
       <c r="A31" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B31" s="5">
         <v>810018</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F31" s="5"/>
-      <c r="G31" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4" t="s">
-        <v>132</v>
-      </c>
+      <c r="G31" s="5"/>
+      <c r="H31" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="I31" s="4"/>
       <c r="J31" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="32" customFormat="1" spans="1:10">
+      <c r="L31" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" spans="1:11">
       <c r="A32" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B32" s="5">
         <v>100005</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="G32" s="4"/>
+        <v>143</v>
+      </c>
+      <c r="G32" s="5"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
-    </row>
-    <row r="33" spans="1:8">
+      <c r="K32" s="4"/>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B33" s="5">
         <v>200008</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="H33" s="13" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" s="14" t="s">
+      <c r="I33" s="22" t="s">
         <v>148</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="13" t="s">
+        <v>149</v>
       </c>
       <c r="B34" s="5">
         <v>600002</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="G34" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="I34" s="4" t="s">
+      <c r="H34" s="14" t="s">
         <v>154</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="35" ht="12" customHeight="1" spans="1:6">
       <c r="A35" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B35" s="5">
         <v>800008</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B36" s="5">
         <v>801003</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="I36" s="4" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="37" spans="1:10">
+      <c r="J36" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B37" s="5">
         <v>200004</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="I37" s="4" t="s">
         <v>169</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="38" customFormat="1" spans="1:10">
+      <c r="K37" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" spans="1:11">
       <c r="A38" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B38" s="5">
         <v>200001</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="G38" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="H38" s="4"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="4" t="s">
+        <v>176</v>
+      </c>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
-    </row>
-    <row r="39" customFormat="1" spans="1:10">
+      <c r="K38" s="4"/>
+    </row>
+    <row r="39" customFormat="1" spans="1:11">
       <c r="A39" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B39" s="5">
         <v>100008</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="G39" s="4"/>
+        <v>180</v>
+      </c>
+      <c r="G39" s="5"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
-    </row>
-    <row r="40" customFormat="1" spans="1:10">
+      <c r="K39" s="4"/>
+    </row>
+    <row r="40" customFormat="1" spans="1:11">
       <c r="A40" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B40" s="5">
         <v>700001</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="G40" s="4"/>
+        <v>183</v>
+      </c>
+      <c r="G40" s="5"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
-    </row>
-    <row r="41" customFormat="1" spans="1:10">
+      <c r="K40" s="4"/>
+    </row>
+    <row r="41" customFormat="1" spans="1:11">
       <c r="A41" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B41" s="5">
         <v>800005</v>
       </c>
       <c r="C41" s="6"/>
       <c r="D41" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="G41" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="H41" s="4"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="4" t="s">
+        <v>188</v>
+      </c>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
-    </row>
-    <row r="42" s="1" customFormat="1" spans="1:10">
+      <c r="K41" s="4"/>
+    </row>
+    <row r="42" s="1" customFormat="1" spans="1:11">
       <c r="A42" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B42" s="5">
         <v>300005</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="G42" s="4"/>
+        <v>193</v>
+      </c>
+      <c r="G42" s="5"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
-      <c r="J42" s="4" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="43" customFormat="1" spans="1:10">
+      <c r="J42" s="4"/>
+      <c r="K42" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" spans="1:11">
       <c r="A43" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B43" s="5">
         <v>300006</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="G43" s="4"/>
+        <v>199</v>
+      </c>
+      <c r="G43" s="5"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
-      <c r="J43" s="4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="44" customFormat="1" ht="17.25" spans="1:10">
+      <c r="J43" s="4"/>
+      <c r="K43" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" ht="17.25" spans="1:11">
       <c r="A44" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B44" s="5">
         <v>100014</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="G44" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="H44" s="4"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="15" t="s">
+        <v>205</v>
+      </c>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
-    </row>
-    <row r="45" customFormat="1" spans="1:10">
+      <c r="K44" s="4"/>
+    </row>
+    <row r="45" customFormat="1" spans="1:11">
       <c r="A45" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B45" s="5">
         <v>200013</v>
       </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="G45" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="H45" s="4"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="4" t="s">
+        <v>210</v>
+      </c>
       <c r="I45" s="4"/>
-      <c r="J45" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="46" customFormat="1" spans="1:10">
+      <c r="J45" s="4"/>
+      <c r="K45" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" spans="1:11">
       <c r="A46" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B46" s="5">
         <v>110008</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="G46" s="4"/>
+        <v>215</v>
+      </c>
+      <c r="G46" s="5"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
-    </row>
-    <row r="47" customFormat="1" spans="1:11">
+      <c r="K46" s="4"/>
+    </row>
+    <row r="47" customFormat="1" spans="1:12">
       <c r="A47" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B47" s="5">
         <v>390001</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="G47" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4" t="s">
+      <c r="G47" s="5"/>
+      <c r="H47" s="16" t="s">
         <v>221</v>
       </c>
+      <c r="I47" s="4"/>
       <c r="J47" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="K47" s="23" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="48" customFormat="1" ht="17.25" spans="1:10">
+      <c r="K47" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="L47" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" ht="17.25" spans="1:11">
       <c r="A48" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B48" s="5">
         <v>400014</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="G48" s="4"/>
+        <v>228</v>
+      </c>
+      <c r="G48" s="5"/>
       <c r="H48" s="4"/>
-      <c r="I48" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="J48" s="4"/>
-    </row>
-    <row r="49" customFormat="1" ht="17.25" spans="1:10">
+      <c r="I48" s="4"/>
+      <c r="J48" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="K48" s="4"/>
+    </row>
+    <row r="49" customFormat="1" ht="17.25" spans="1:11">
       <c r="A49" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B49" s="5">
         <v>500004</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="G49" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="H49" s="4"/>
-      <c r="I49" s="24" t="s">
+      <c r="G49" s="5"/>
+      <c r="H49" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="J49" s="4"/>
-    </row>
-    <row r="50" customFormat="1" ht="16" customHeight="1" spans="1:10">
+      <c r="I49" s="4"/>
+      <c r="J49" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="K49" s="4"/>
+    </row>
+    <row r="50" customFormat="1" ht="16" customHeight="1" spans="1:11">
       <c r="A50" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B50" s="5">
         <v>100001</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="G50" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="H50" s="4"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="4" t="s">
+        <v>241</v>
+      </c>
       <c r="I50" s="4"/>
-      <c r="J50" s="4" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="51" customFormat="1" spans="1:10">
+      <c r="J50" s="4"/>
+      <c r="K50" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" spans="1:11">
       <c r="A51" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B51" s="5">
         <v>120004</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="G51" s="4"/>
+        <v>246</v>
+      </c>
+      <c r="G51" s="5"/>
       <c r="H51" s="4"/>
-      <c r="I51" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="J51" s="4"/>
-    </row>
-    <row r="52" customFormat="1" spans="1:10">
+      <c r="I51" s="4"/>
+      <c r="J51" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="K51" s="4"/>
+    </row>
+    <row r="52" customFormat="1" spans="1:11">
       <c r="A52" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B52" s="5">
         <v>710018</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="G52" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4" t="s">
+      <c r="G52" s="5"/>
+      <c r="H52" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="J52" s="4"/>
-    </row>
-    <row r="53" customFormat="1" spans="1:14">
+      <c r="I52" s="4"/>
+      <c r="J52" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="K52" s="4"/>
+    </row>
+    <row r="53" customFormat="1" spans="1:15">
       <c r="A53" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B53" s="5">
         <v>100012</v>
       </c>
       <c r="C53" s="6"/>
       <c r="D53" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="G53" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4" t="s">
+      <c r="G53" s="5"/>
+      <c r="H53" s="17" t="s">
         <v>258</v>
       </c>
+      <c r="I53" s="4"/>
       <c r="J53" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="L53" t="s">
+      <c r="K53" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="N53" t="s">
+      <c r="M53" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="54" customFormat="1" spans="1:11">
+      <c r="O53" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" spans="1:12">
       <c r="A54" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B54" s="5">
         <v>100012</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="G54" s="19" t="s">
         <v>267</v>
       </c>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4" t="s">
+      <c r="G54" s="5"/>
+      <c r="H54" s="18" t="s">
         <v>268</v>
       </c>
+      <c r="I54" s="4"/>
       <c r="J54" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="K54" t="s">
+      <c r="K54" s="4" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="55" customFormat="1" spans="1:10">
+      <c r="L54" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" spans="1:11">
       <c r="A55" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B55" s="5">
         <v>390021</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="G55" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="H55" s="4"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="19" t="s">
+        <v>277</v>
+      </c>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
-    </row>
-    <row r="56" customFormat="1" spans="1:10">
+      <c r="K55" s="4"/>
+    </row>
+    <row r="56" customFormat="1" spans="1:11">
       <c r="A56" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B56" s="5">
         <v>300007</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="G56" s="4" t="s">
         <v>282</v>
       </c>
+      <c r="G56" s="5"/>
       <c r="H56" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4" t="s">
+      <c r="I56" s="4" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="57" customFormat="1" spans="1:10">
+      <c r="J56" s="4"/>
+      <c r="K56" s="4" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="57" customFormat="1" spans="1:11">
       <c r="A57" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B57" s="5">
         <v>400036</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="G57" s="4" t="s">
         <v>290</v>
       </c>
+      <c r="G57" s="5"/>
       <c r="H57" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="I57" s="4"/>
+      <c r="I57" s="4" t="s">
+        <v>292</v>
+      </c>
       <c r="J57" s="4"/>
-    </row>
-    <row r="58" customFormat="1" spans="1:10">
+      <c r="K57" s="4"/>
+    </row>
+    <row r="58" customFormat="1" spans="1:11">
       <c r="A58" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B58" s="5">
         <v>330001</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="G58" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4" t="s">
+      <c r="G58" s="5"/>
+      <c r="H58" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="J58" s="4"/>
-    </row>
-    <row r="59" customFormat="1" spans="1:10">
+      <c r="I58" s="4"/>
+      <c r="J58" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="K58" s="4"/>
+    </row>
+    <row r="59" customFormat="1" spans="1:11">
       <c r="A59" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B59" s="5">
         <v>600001</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="G59" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="H59" s="4"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="4" t="s">
+        <v>305</v>
+      </c>
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
-    </row>
-    <row r="60" customFormat="1" spans="1:10">
+      <c r="K59" s="4"/>
+    </row>
+    <row r="60" customFormat="1" spans="1:11">
       <c r="A60" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B60" s="5">
         <v>600023</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="G60" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="H60" s="4"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="4" t="s">
+        <v>311</v>
+      </c>
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
-    </row>
-    <row r="61" customFormat="1" spans="1:10">
+      <c r="K60" s="4"/>
+    </row>
+    <row r="61" customFormat="1" spans="1:11">
       <c r="A61" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B61" s="5">
         <v>400015</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="G61" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="H61" s="4"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="4" t="s">
+        <v>317</v>
+      </c>
       <c r="I61" s="4"/>
       <c r="J61" s="4"/>
-    </row>
-    <row r="62" customFormat="1" spans="1:10">
+      <c r="K61" s="4"/>
+    </row>
+    <row r="62" customFormat="1" spans="1:11">
       <c r="A62" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B62" s="5">
         <v>100015</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="G62" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="H62" s="5"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4" t="s">
+      <c r="G62" s="5"/>
+      <c r="H62" s="4" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="63" customFormat="1" spans="1:10">
+      <c r="I62" s="5"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" spans="1:11">
       <c r="A63" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B63" s="5">
         <v>100006</v>
       </c>
       <c r="C63" s="6"/>
       <c r="D63" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="G63" s="4"/>
+        <v>327</v>
+      </c>
+      <c r="G63" s="5"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
       <c r="J63" s="4"/>
-    </row>
-    <row r="64" customFormat="1" spans="1:10">
+      <c r="K63" s="4"/>
+    </row>
+    <row r="64" customFormat="1" spans="1:11">
       <c r="A64" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B64" s="5">
         <v>200005</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="G64" s="4"/>
+        <v>331</v>
+      </c>
+      <c r="G64" s="5"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
-    </row>
-    <row r="65" customFormat="1" spans="1:10">
+      <c r="K64" s="4"/>
+    </row>
+    <row r="65" customFormat="1" spans="1:11">
       <c r="A65" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B65" s="5">
         <v>710006</v>
       </c>
       <c r="C65" s="6"/>
       <c r="D65" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="G65" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="H65" s="4"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="4" t="s">
+        <v>336</v>
+      </c>
       <c r="I65" s="4"/>
       <c r="J65" s="4"/>
-    </row>
-    <row r="66" customFormat="1" spans="1:11">
+      <c r="K65" s="4"/>
+    </row>
+    <row r="66" customFormat="1" spans="1:12">
       <c r="A66" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B66" s="5">
         <v>100013</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="G66" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="H66" s="4"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="4" t="s">
+        <v>341</v>
+      </c>
       <c r="I66" s="4"/>
       <c r="J66" s="4"/>
-      <c r="K66" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="67" customFormat="1" spans="1:10">
+      <c r="K66" s="4"/>
+      <c r="L66" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="67" customFormat="1" spans="1:11">
       <c r="A67" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B67" s="5">
         <v>100018</v>
       </c>
       <c r="C67" s="6"/>
       <c r="D67" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="G67" s="4" t="s">
         <v>346</v>
       </c>
+      <c r="G67" s="5"/>
       <c r="H67" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="I67" s="4"/>
+      <c r="I67" s="4" t="s">
+        <v>348</v>
+      </c>
       <c r="J67" s="4"/>
-    </row>
-    <row r="68" customFormat="1" spans="1:10">
+      <c r="K67" s="4"/>
+    </row>
+    <row r="68" customFormat="1" spans="1:11">
       <c r="A68" s="5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B68" s="5">
         <v>200012</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="G68" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="H68" s="4"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="4" t="s">
+        <v>353</v>
+      </c>
       <c r="I68" s="4"/>
       <c r="J68" s="4"/>
-    </row>
-    <row r="69" customFormat="1" spans="1:10">
+      <c r="K68" s="4"/>
+    </row>
+    <row r="69" customFormat="1" spans="1:11">
       <c r="A69" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B69" s="5">
         <v>232001</v>
       </c>
       <c r="C69" s="6"/>
       <c r="D69" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="G69" s="4"/>
+        <v>357</v>
+      </c>
+      <c r="G69" s="5"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
       <c r="J69" s="4"/>
-    </row>
-    <row r="70" customFormat="1" spans="1:10">
+      <c r="K69" s="4"/>
+    </row>
+    <row r="70" customFormat="1" spans="1:11">
       <c r="A70" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B70" s="5">
         <v>790006</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="G70" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4" t="s">
+      <c r="G70" s="5"/>
+      <c r="H70" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="J70" s="4"/>
-    </row>
-    <row r="71" customFormat="1" spans="1:10">
+      <c r="I70" s="4"/>
+      <c r="J70" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="K70" s="4"/>
+    </row>
+    <row r="71" customFormat="1" spans="1:11">
       <c r="A71" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B71" s="5">
         <v>800016</v>
       </c>
       <c r="C71" s="6"/>
       <c r="D71" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="G71" s="4" t="s">
         <v>366</v>
       </c>
+      <c r="G71" s="5"/>
       <c r="H71" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="I71" s="4"/>
-      <c r="J71" s="4" t="s">
+      <c r="I71" s="4" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="72" customFormat="1" spans="1:10">
+      <c r="J71" s="4"/>
+      <c r="K71" s="4" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="72" customFormat="1" spans="1:11">
       <c r="A72" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B72" s="5">
         <v>600011</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="H72" s="4"/>
+        <v>374</v>
+      </c>
+      <c r="G72" s="5"/>
+      <c r="H72" s="4" t="s">
+        <v>317</v>
+      </c>
       <c r="I72" s="4"/>
       <c r="J72" s="4"/>
-    </row>
-    <row r="73" customFormat="1" spans="1:10">
+      <c r="K72" s="4"/>
+    </row>
+    <row r="73" customFormat="1" spans="1:11">
       <c r="A73" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B73" s="5">
         <v>600003</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="G73" s="4"/>
+        <v>379</v>
+      </c>
+      <c r="G73" s="5"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
       <c r="J73" s="4"/>
-    </row>
-    <row r="74" customFormat="1" spans="1:10">
+      <c r="K73" s="4"/>
+    </row>
+    <row r="74" customFormat="1" spans="1:11">
       <c r="A74" s="5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B74" s="5">
         <v>600007</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="G74" s="4"/>
+        <v>384</v>
+      </c>
+      <c r="G74" s="5"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
       <c r="J74" s="4"/>
-    </row>
-    <row r="75" customFormat="1" ht="15" customHeight="1" spans="1:10">
+      <c r="K74" s="4"/>
+    </row>
+    <row r="75" customFormat="1" ht="15" customHeight="1" spans="1:11">
       <c r="A75" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B75" s="5">
         <v>600015</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="G75" s="4"/>
+        <v>389</v>
+      </c>
+      <c r="G75" s="5"/>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
       <c r="J75" s="4"/>
-    </row>
-    <row r="76" customFormat="1" spans="1:10">
+      <c r="K75" s="4"/>
+    </row>
+    <row r="76" customFormat="1" spans="1:11">
       <c r="A76" s="5" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B76" s="5">
         <v>600021</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="G76" s="4"/>
+        <v>394</v>
+      </c>
+      <c r="G76" s="5"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
       <c r="J76" s="4"/>
-    </row>
-    <row r="77" customFormat="1" spans="1:10">
+      <c r="K76" s="4"/>
+    </row>
+    <row r="77" customFormat="1" spans="1:11">
       <c r="A77" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B77" s="5">
         <v>600025</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="G77" s="4"/>
+        <v>399</v>
+      </c>
+      <c r="G77" s="5"/>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
-    </row>
-    <row r="78" customFormat="1" spans="1:10">
+      <c r="K77" s="4"/>
+    </row>
+    <row r="78" customFormat="1" spans="1:11">
       <c r="A78" s="5" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B78" s="5">
         <v>300004</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="G78" s="4"/>
+        <v>404</v>
+      </c>
+      <c r="G78" s="5"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
       <c r="J78" s="4"/>
-    </row>
-    <row r="79" customFormat="1" spans="1:10">
+      <c r="K78" s="4"/>
+    </row>
+    <row r="79" customFormat="1" spans="1:11">
       <c r="A79" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B79" s="5">
         <v>330002</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="G79" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4" t="s">
+      <c r="G79" s="5"/>
+      <c r="H79" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="J79" s="4"/>
-    </row>
-    <row r="80" customFormat="1" spans="1:14">
+      <c r="I79" s="4"/>
+      <c r="J79" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="K79" s="4"/>
+    </row>
+    <row r="80" customFormat="1" spans="1:15">
       <c r="A80" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B80" s="5">
         <v>390002</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="G80" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4" t="s">
+      <c r="G80" s="5"/>
+      <c r="H80" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="J80" s="19" t="s">
+      <c r="I80" s="4"/>
+      <c r="J80" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="K80" t="s">
+      <c r="K80" s="18" t="s">
         <v>419</v>
       </c>
       <c r="L80" t="s">
         <v>420</v>
       </c>
-      <c r="N80" t="s">
+      <c r="M80" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="81" customFormat="1" spans="1:10">
+      <c r="O80" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="81" customFormat="1" spans="1:11">
       <c r="A81" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B81" s="5">
         <v>590003</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="G81" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="H81" s="4"/>
-      <c r="I81" s="4" t="s">
+      <c r="G81" s="5"/>
+      <c r="H81" s="4" t="s">
         <v>428</v>
       </c>
+      <c r="I81" s="4"/>
       <c r="J81" s="4" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="82" s="2" customFormat="1" spans="1:10">
+      <c r="K81" s="4" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="82" s="2" customFormat="1" spans="1:11">
       <c r="A82" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B82" s="5">
         <v>590006</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="G82" s="25" t="s">
         <v>435</v>
       </c>
-      <c r="H82" s="25"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="25" t="s">
+        <v>436</v>
+      </c>
       <c r="I82" s="25"/>
-      <c r="J82" s="25" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="83" s="2" customFormat="1" spans="1:10">
-      <c r="A83" s="20" t="s">
+      <c r="J82" s="25"/>
+      <c r="K82" s="25" t="s">
         <v>437</v>
+      </c>
+    </row>
+    <row r="83" s="2" customFormat="1" spans="1:11">
+      <c r="A83" s="19" t="s">
+        <v>438</v>
       </c>
       <c r="B83" s="5">
         <v>400005</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="G83" s="25" t="s">
         <v>442</v>
       </c>
-      <c r="H83" s="25"/>
-      <c r="I83" s="25" t="s">
+      <c r="G83" s="5"/>
+      <c r="H83" s="25" t="s">
         <v>443</v>
       </c>
+      <c r="I83" s="25"/>
       <c r="J83" s="25" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="84" s="2" customFormat="1" spans="1:10">
+      <c r="K83" s="25" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="84" s="2" customFormat="1" spans="1:11">
       <c r="A84" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B84" s="5">
         <v>400006</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="G84" s="25"/>
+        <v>450</v>
+      </c>
+      <c r="G84" s="5"/>
       <c r="H84" s="25"/>
       <c r="I84" s="25"/>
       <c r="J84" s="25"/>
-    </row>
-    <row r="85" s="2" customFormat="1" spans="1:10">
+      <c r="K84" s="25"/>
+    </row>
+    <row r="85" s="2" customFormat="1" spans="1:11">
       <c r="A85" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B85" s="5">
         <v>400020</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="G85" s="25" t="s">
         <v>455</v>
       </c>
-      <c r="H85" s="25"/>
+      <c r="G85" s="5"/>
+      <c r="H85" s="25" t="s">
+        <v>456</v>
+      </c>
       <c r="I85" s="25"/>
       <c r="J85" s="25"/>
-    </row>
-    <row r="86" s="3" customFormat="1" spans="1:10">
+      <c r="K85" s="25"/>
+    </row>
+    <row r="86" s="3" customFormat="1" spans="1:11">
       <c r="A86" s="26" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B86" s="5">
         <v>450018</v>
       </c>
       <c r="C86" s="26" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D86" s="26" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F86" s="5"/>
-      <c r="G86" s="27"/>
+      <c r="G86" s="5"/>
       <c r="H86" s="27"/>
       <c r="I86" s="27"/>
       <c r="J86" s="27"/>
-    </row>
-    <row r="87" s="3" customFormat="1" spans="1:10">
+      <c r="K86" s="27"/>
+    </row>
+    <row r="87" s="3" customFormat="1" spans="1:11">
       <c r="A87" s="26" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B87" s="5">
         <v>450019</v>
       </c>
       <c r="C87" s="26" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D87" s="26" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F87" s="5"/>
-      <c r="G87" s="27"/>
+      <c r="G87" s="5"/>
       <c r="H87" s="27"/>
       <c r="I87" s="27"/>
       <c r="J87" s="27"/>
-    </row>
-    <row r="88" s="2" customFormat="1" spans="1:10">
+      <c r="K87" s="27"/>
+    </row>
+    <row r="88" s="2" customFormat="1" spans="1:11">
       <c r="A88" s="6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B88" s="5">
         <v>400024</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>468</v>
-      </c>
-      <c r="G88" s="25" t="s">
         <v>469</v>
       </c>
-      <c r="H88" s="25"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="25" t="s">
+        <v>470</v>
+      </c>
       <c r="I88" s="25"/>
       <c r="J88" s="25"/>
-    </row>
-    <row r="89" s="2" customFormat="1" spans="1:10">
+      <c r="K88" s="25"/>
+    </row>
+    <row r="89" s="2" customFormat="1" spans="1:11">
       <c r="A89" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B89" s="5">
         <v>400044</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="G89" s="25"/>
+        <v>475</v>
+      </c>
+      <c r="G89" s="5"/>
       <c r="H89" s="25"/>
       <c r="I89" s="25"/>
       <c r="J89" s="25"/>
-    </row>
-    <row r="90" s="2" customFormat="1" spans="1:10">
+      <c r="K89" s="25"/>
+    </row>
+    <row r="90" s="2" customFormat="1" spans="1:11">
       <c r="A90" s="6" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B90" s="5">
         <v>400047</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>479</v>
-      </c>
-      <c r="G90" s="25" t="s">
         <v>480</v>
       </c>
-      <c r="H90" s="25"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="25" t="s">
+        <v>481</v>
+      </c>
       <c r="I90" s="25"/>
-      <c r="J90" s="25" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="91" s="2" customFormat="1" spans="1:10">
+      <c r="J90" s="25"/>
+      <c r="K90" s="25" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="91" s="2" customFormat="1" spans="1:11">
       <c r="A91" s="6" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B91" s="5">
         <v>490037</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="G91" s="25"/>
+        <v>487</v>
+      </c>
+      <c r="G91" s="5"/>
       <c r="H91" s="25"/>
       <c r="I91" s="25"/>
       <c r="J91" s="25"/>
-    </row>
-    <row r="92" s="2" customFormat="1" spans="1:10">
+      <c r="K91" s="25"/>
+    </row>
+    <row r="92" s="2" customFormat="1" spans="1:11">
       <c r="A92" s="6" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B92" s="5">
         <v>490021</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="G92" s="25"/>
+        <v>492</v>
+      </c>
+      <c r="G92" s="5"/>
       <c r="H92" s="25"/>
       <c r="I92" s="25"/>
       <c r="J92" s="25"/>
-    </row>
-    <row r="93" s="2" customFormat="1" spans="1:10">
+      <c r="K92" s="25"/>
+    </row>
+    <row r="93" s="2" customFormat="1" spans="1:11">
       <c r="A93" s="6" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B93" s="5">
         <v>400040</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="G93" s="25" t="s">
         <v>497</v>
       </c>
-      <c r="H93" s="25"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="25" t="s">
+        <v>498</v>
+      </c>
       <c r="I93" s="25"/>
       <c r="J93" s="25"/>
-    </row>
-    <row r="94" s="2" customFormat="1" spans="1:10">
+      <c r="K93" s="25"/>
+    </row>
+    <row r="94" s="2" customFormat="1" spans="1:11">
       <c r="A94" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B94" s="5">
         <v>200002</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>501</v>
-      </c>
-      <c r="G94" s="25" t="s">
         <v>502</v>
       </c>
-      <c r="H94" s="25"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="25" t="s">
+        <v>503</v>
+      </c>
       <c r="I94" s="25"/>
       <c r="J94" s="25"/>
-    </row>
-    <row r="95" s="2" customFormat="1" spans="1:10">
+      <c r="K94" s="25"/>
+    </row>
+    <row r="95" s="2" customFormat="1" spans="1:11">
       <c r="A95" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B95" s="5">
         <v>200011</v>
       </c>
       <c r="C95" s="6"/>
       <c r="D95" s="6" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>506</v>
-      </c>
-      <c r="G95" s="25"/>
+        <v>507</v>
+      </c>
+      <c r="G95" s="5"/>
       <c r="H95" s="25"/>
-      <c r="I95" s="5"/>
-      <c r="J95" s="25"/>
-    </row>
-    <row r="96" s="2" customFormat="1" spans="1:10">
+      <c r="I95" s="25"/>
+      <c r="J95" s="5"/>
+      <c r="K95" s="25"/>
+    </row>
+    <row r="96" s="2" customFormat="1" spans="1:11">
       <c r="A96" s="6" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B96" s="5">
         <v>200016</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="6" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>510</v>
-      </c>
-      <c r="G96" s="25" t="s">
         <v>511</v>
       </c>
-      <c r="H96" s="25"/>
-      <c r="I96" s="5"/>
-      <c r="J96" s="25"/>
-    </row>
-    <row r="97" s="2" customFormat="1" spans="1:10">
+      <c r="G96" s="5"/>
+      <c r="H96" s="25" t="s">
+        <v>512</v>
+      </c>
+      <c r="I96" s="25"/>
+      <c r="J96" s="5"/>
+      <c r="K96" s="25"/>
+    </row>
+    <row r="97" s="2" customFormat="1" spans="1:11">
       <c r="A97" s="6" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B97" s="5">
         <v>200017</v>
       </c>
       <c r="C97" s="6"/>
       <c r="D97" s="6" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="G97" s="25"/>
+        <v>516</v>
+      </c>
+      <c r="G97" s="5"/>
       <c r="H97" s="25"/>
-      <c r="I97" s="5"/>
-      <c r="J97" s="25"/>
-    </row>
-    <row r="98" s="2" customFormat="1" spans="1:10">
+      <c r="I97" s="25"/>
+      <c r="J97" s="5"/>
+      <c r="K97" s="25"/>
+    </row>
+    <row r="98" s="2" customFormat="1" spans="1:11">
       <c r="A98" s="6" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B98" s="5">
         <v>100007</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>518</v>
-      </c>
-      <c r="G98" s="25" t="s">
         <v>519</v>
       </c>
+      <c r="G98" s="5"/>
       <c r="H98" s="25" t="s">
         <v>520</v>
       </c>
-      <c r="I98" s="5"/>
-      <c r="J98" s="25"/>
-    </row>
-    <row r="99" s="2" customFormat="1" spans="1:10">
+      <c r="I98" s="25" t="s">
+        <v>521</v>
+      </c>
+      <c r="J98" s="5"/>
+      <c r="K98" s="25"/>
+    </row>
+    <row r="99" s="2" customFormat="1" spans="1:11">
       <c r="A99" s="6" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B99" s="5">
         <v>100011</v>
       </c>
       <c r="C99" s="6"/>
       <c r="D99" s="6" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="G99" s="25" t="s">
         <v>525</v>
       </c>
-      <c r="H99" s="25"/>
-      <c r="I99" s="5"/>
-      <c r="J99" s="4" t="s">
+      <c r="G99" s="5"/>
+      <c r="H99" s="25" t="s">
         <v>526</v>
       </c>
-    </row>
-    <row r="100" s="2" customFormat="1" spans="1:10">
+      <c r="I99" s="25"/>
+      <c r="J99" s="5"/>
+      <c r="K99" s="4" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="100" s="2" customFormat="1" spans="1:11">
       <c r="A100" s="6" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B100" s="5">
         <v>700004</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>530</v>
-      </c>
-      <c r="G100" s="25" t="s">
         <v>531</v>
       </c>
+      <c r="G100" s="5"/>
       <c r="H100" s="25" t="s">
         <v>532</v>
       </c>
-      <c r="I100" s="5" t="s">
+      <c r="I100" s="25" t="s">
         <v>533</v>
       </c>
-      <c r="J100" s="25"/>
-    </row>
-    <row r="101" s="2" customFormat="1" spans="1:10">
+      <c r="J100" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="K100" s="25"/>
+    </row>
+    <row r="101" s="2" customFormat="1" spans="1:11">
       <c r="A101" s="6" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B101" s="5">
         <v>710029</v>
       </c>
       <c r="C101" s="6"/>
       <c r="D101" s="6" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>537</v>
-      </c>
-      <c r="G101" s="25" t="s">
         <v>538</v>
       </c>
-      <c r="H101" s="25"/>
-      <c r="I101" s="5"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="25" t="s">
+        <v>539</v>
+      </c>
+      <c r="I101" s="25"/>
       <c r="J101" s="5"/>
-    </row>
-    <row r="102" s="2" customFormat="1" spans="1:10">
+      <c r="K101" s="5"/>
+    </row>
+    <row r="102" s="2" customFormat="1" spans="1:11">
       <c r="A102" s="6" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B102" s="5">
         <v>800019</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="6" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="G102" s="25" t="s">
         <v>543</v>
       </c>
-      <c r="H102" s="25"/>
-      <c r="I102" s="5" t="s">
+      <c r="G102" s="5"/>
+      <c r="H102" s="25" t="s">
         <v>544</v>
       </c>
+      <c r="I102" s="25"/>
       <c r="J102" s="5" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="103" s="2" customFormat="1" spans="1:12">
+      <c r="K102" s="5" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="103" s="2" customFormat="1" spans="1:13">
       <c r="A103" s="6" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B103" s="5">
         <v>801002</v>
       </c>
       <c r="C103" s="6"/>
       <c r="D103" s="6" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="G103" s="25" t="s">
         <v>550</v>
       </c>
+      <c r="G103" s="5"/>
       <c r="H103" s="25" t="s">
         <v>551</v>
       </c>
-      <c r="I103" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="J103" s="25" t="s">
+      <c r="I103" s="25" t="s">
         <v>552</v>
       </c>
-      <c r="K103" s="2" t="s">
+      <c r="J103" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="K103" s="25" t="s">
         <v>553</v>
       </c>
       <c r="L103" s="2" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="104" s="2" customFormat="1" spans="1:10">
+      <c r="M103" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="104" s="2" customFormat="1" spans="1:11">
       <c r="A104" s="6" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B104" s="5">
         <v>800010</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="6" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>558</v>
-      </c>
-      <c r="G104" s="25"/>
+        <v>559</v>
+      </c>
+      <c r="G104" s="5"/>
       <c r="H104" s="25"/>
-      <c r="I104" s="5"/>
-      <c r="J104" s="25"/>
-    </row>
-    <row r="105" s="2" customFormat="1" spans="1:10">
+      <c r="I104" s="25"/>
+      <c r="J104" s="5"/>
+      <c r="K104" s="25"/>
+    </row>
+    <row r="105" s="2" customFormat="1" spans="1:11">
       <c r="A105" s="6" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B105" s="5">
         <v>800011</v>
       </c>
       <c r="C105" s="6"/>
       <c r="D105" s="6" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>562</v>
-      </c>
-      <c r="G105" s="25"/>
+        <v>563</v>
+      </c>
+      <c r="G105" s="5"/>
       <c r="H105" s="25"/>
-      <c r="I105" s="5"/>
-      <c r="J105" s="25"/>
-    </row>
-    <row r="106" s="2" customFormat="1" spans="1:13">
+      <c r="I105" s="25"/>
+      <c r="J105" s="5"/>
+      <c r="K105" s="25"/>
+    </row>
+    <row r="106" s="2" customFormat="1" spans="1:14">
       <c r="A106" s="6" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B106" s="5">
         <v>800015</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="G106" s="25" t="s">
         <v>568</v>
       </c>
+      <c r="G106" s="5"/>
       <c r="H106" s="25" t="s">
         <v>569</v>
       </c>
@@ -6654,1208 +6740,1263 @@
       <c r="J106" s="25" t="s">
         <v>571</v>
       </c>
-      <c r="K106" s="2" t="s">
+      <c r="K106" s="25" t="s">
         <v>572</v>
       </c>
-      <c r="M106" s="2" t="s">
+      <c r="L106" s="2" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="107" s="2" customFormat="1" spans="1:10">
+      <c r="N106" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="107" s="2" customFormat="1" spans="1:11">
       <c r="A107" s="6" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B107" s="5">
         <v>800018</v>
       </c>
       <c r="C107" s="6"/>
       <c r="D107" s="6" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>577</v>
-      </c>
-      <c r="G107" s="25" t="s">
         <v>578</v>
       </c>
-      <c r="H107" s="4" t="s">
+      <c r="G107" s="5"/>
+      <c r="H107" s="25" t="s">
         <v>579</v>
       </c>
-      <c r="I107" s="25"/>
-      <c r="J107" s="6"/>
-    </row>
-    <row r="108" s="2" customFormat="1" spans="1:10">
+      <c r="I107" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="J107" s="25"/>
+      <c r="K107" s="6"/>
+    </row>
+    <row r="108" s="2" customFormat="1" spans="1:11">
       <c r="A108" s="6" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B108" s="5">
         <v>800021</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="6" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>583</v>
-      </c>
-      <c r="G108" s="6"/>
-      <c r="H108" s="25"/>
-      <c r="I108" s="25" t="s">
         <v>584</v>
       </c>
-      <c r="J108" s="25"/>
-    </row>
-    <row r="109" s="2" customFormat="1" spans="1:10">
+      <c r="G108" s="5"/>
+      <c r="H108" s="6"/>
+      <c r="I108" s="25"/>
+      <c r="J108" s="25" t="s">
+        <v>585</v>
+      </c>
+      <c r="K108" s="25"/>
+    </row>
+    <row r="109" s="2" customFormat="1" spans="1:11">
       <c r="A109" s="6" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B109" s="5">
         <v>800028</v>
       </c>
       <c r="C109" s="6"/>
       <c r="D109" s="6" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>588</v>
-      </c>
-      <c r="G109" s="25"/>
-      <c r="H109" s="6"/>
-      <c r="I109" s="25"/>
+        <v>589</v>
+      </c>
+      <c r="G109" s="5"/>
+      <c r="H109" s="25"/>
+      <c r="I109" s="6"/>
       <c r="J109" s="25"/>
-    </row>
-    <row r="110" s="2" customFormat="1" ht="16" customHeight="1" spans="1:10">
+      <c r="K109" s="25"/>
+    </row>
+    <row r="110" s="2" customFormat="1" ht="16" customHeight="1" spans="1:11">
       <c r="A110" s="6" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B110" s="5">
         <v>800017</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="6" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>592</v>
-      </c>
-      <c r="G110" s="25" t="s">
         <v>593</v>
       </c>
-      <c r="H110" s="25"/>
-      <c r="I110" s="6" t="s">
+      <c r="G110" s="5"/>
+      <c r="H110" s="25" t="s">
         <v>594</v>
       </c>
-      <c r="J110" s="18" t="s">
+      <c r="I110" s="25"/>
+      <c r="J110" s="6" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="111" s="2" customFormat="1" spans="1:10">
+      <c r="K110" s="17" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="111" s="2" customFormat="1" spans="1:11">
       <c r="A111" s="6" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B111" s="5">
         <v>800026</v>
       </c>
       <c r="C111" s="6"/>
       <c r="D111" s="6" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>599</v>
-      </c>
-      <c r="G111" s="25"/>
+        <v>600</v>
+      </c>
+      <c r="G111" s="5"/>
       <c r="H111" s="25"/>
       <c r="I111" s="25"/>
       <c r="J111" s="25"/>
-    </row>
-    <row r="112" s="2" customFormat="1" spans="1:10">
+      <c r="K111" s="25"/>
+    </row>
+    <row r="112" s="2" customFormat="1" spans="1:11">
       <c r="A112" s="6" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B112" s="5">
         <v>800027</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="6" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>603</v>
-      </c>
-      <c r="G112" s="25"/>
+        <v>604</v>
+      </c>
+      <c r="G112" s="5"/>
       <c r="H112" s="25"/>
       <c r="I112" s="25"/>
       <c r="J112" s="25"/>
-    </row>
-    <row r="113" s="2" customFormat="1" spans="1:10">
+      <c r="K112" s="25"/>
+    </row>
+    <row r="113" s="2" customFormat="1" spans="1:11">
       <c r="A113" s="6" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B113" s="5">
         <v>710031</v>
       </c>
       <c r="C113" s="6"/>
       <c r="D113" s="6" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="G113" s="25"/>
+        <v>608</v>
+      </c>
+      <c r="G113" s="5"/>
       <c r="H113" s="25"/>
       <c r="I113" s="25"/>
-      <c r="J113" s="6"/>
-    </row>
-    <row r="114" s="2" customFormat="1" spans="1:10">
+      <c r="J113" s="25"/>
+      <c r="K113" s="6"/>
+    </row>
+    <row r="114" s="2" customFormat="1" spans="1:11">
       <c r="A114" s="6" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B114" s="5">
         <v>790029</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="6" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>610</v>
-      </c>
-      <c r="G114" s="25"/>
+        <v>611</v>
+      </c>
+      <c r="G114" s="5"/>
       <c r="H114" s="25"/>
       <c r="I114" s="25"/>
       <c r="J114" s="25"/>
-    </row>
-    <row r="115" s="2" customFormat="1" spans="1:13">
+      <c r="K114" s="25"/>
+    </row>
+    <row r="115" s="2" customFormat="1" spans="1:14">
       <c r="A115" s="6" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B115" s="5">
         <v>710001</v>
       </c>
       <c r="C115" s="6"/>
       <c r="D115" s="6" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>614</v>
-      </c>
-      <c r="G115" s="25" t="s">
         <v>615</v>
       </c>
-      <c r="H115" s="25"/>
-      <c r="I115" s="25" t="s">
+      <c r="G115" s="5"/>
+      <c r="H115" s="25" t="s">
         <v>616</v>
       </c>
-      <c r="J115" s="25"/>
-      <c r="K115" s="2" t="s">
+      <c r="I115" s="25"/>
+      <c r="J115" s="25" t="s">
         <v>617</v>
       </c>
-      <c r="M115" s="2" t="s">
+      <c r="K115" s="25"/>
+      <c r="L115" s="2" t="s">
         <v>618</v>
       </c>
-    </row>
-    <row r="116" s="2" customFormat="1" spans="1:11">
+      <c r="N115" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="116" s="2" customFormat="1" spans="1:12">
       <c r="A116" s="6" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B116" s="5">
         <v>710002</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="6" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>622</v>
-      </c>
-      <c r="G116" s="25" t="s">
         <v>623</v>
       </c>
-      <c r="H116" s="25"/>
+      <c r="G116" s="5"/>
+      <c r="H116" s="25" t="s">
+        <v>624</v>
+      </c>
       <c r="I116" s="25"/>
-      <c r="J116" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="K116" s="29"/>
-    </row>
-    <row r="117" s="2" customFormat="1" spans="1:10">
+      <c r="J116" s="25"/>
+      <c r="K116" s="25" t="s">
+        <v>625</v>
+      </c>
+      <c r="L116" s="29"/>
+    </row>
+    <row r="117" s="2" customFormat="1" spans="1:11">
       <c r="A117" s="6" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B117" s="5">
         <v>710003</v>
       </c>
       <c r="C117" s="6"/>
       <c r="D117" s="6" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>628</v>
-      </c>
-      <c r="G117" s="25" t="s">
         <v>629</v>
       </c>
+      <c r="G117" s="5"/>
       <c r="H117" s="25" t="s">
         <v>630</v>
       </c>
-      <c r="I117" s="25"/>
-      <c r="J117" s="5"/>
-    </row>
-    <row r="118" s="2" customFormat="1" spans="1:10">
+      <c r="I117" s="25" t="s">
+        <v>631</v>
+      </c>
+      <c r="J117" s="25"/>
+      <c r="K117" s="5"/>
+    </row>
+    <row r="118" s="2" customFormat="1" spans="1:11">
       <c r="A118" s="6" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B118" s="5">
         <v>710033</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="4" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>634</v>
-      </c>
-      <c r="G118" s="20" t="s">
         <v>635</v>
       </c>
-      <c r="H118" s="25"/>
+      <c r="G118" s="5"/>
+      <c r="H118" s="19" t="s">
+        <v>636</v>
+      </c>
       <c r="I118" s="25"/>
-      <c r="J118" s="5"/>
-    </row>
-    <row r="119" s="2" customFormat="1" spans="1:10">
+      <c r="J118" s="25"/>
+      <c r="K118" s="5"/>
+    </row>
+    <row r="119" s="2" customFormat="1" spans="1:11">
       <c r="A119" s="6" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B119" s="5">
         <v>790001</v>
       </c>
       <c r="C119" s="6"/>
       <c r="D119" s="6" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>638</v>
-      </c>
-      <c r="G119" s="25"/>
+        <v>639</v>
+      </c>
+      <c r="G119" s="5"/>
       <c r="H119" s="25"/>
       <c r="I119" s="25"/>
       <c r="J119" s="25"/>
-    </row>
-    <row r="120" s="2" customFormat="1" spans="1:10">
+      <c r="K119" s="25"/>
+    </row>
+    <row r="120" s="2" customFormat="1" spans="1:11">
       <c r="A120" s="6" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B120" s="5">
         <v>710019</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="6" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>642</v>
-      </c>
-      <c r="G120" s="25"/>
+        <v>643</v>
+      </c>
+      <c r="G120" s="5"/>
       <c r="H120" s="25"/>
-      <c r="I120" s="6"/>
-      <c r="J120" s="25"/>
-    </row>
-    <row r="121" s="2" customFormat="1" spans="1:10">
+      <c r="I120" s="25"/>
+      <c r="J120" s="6"/>
+      <c r="K120" s="25"/>
+    </row>
+    <row r="121" s="2" customFormat="1" spans="1:11">
       <c r="A121" s="6" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B121" s="5">
         <v>230001</v>
       </c>
       <c r="C121" s="6"/>
       <c r="D121" s="6" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>646</v>
-      </c>
-      <c r="G121" s="25" t="s">
         <v>647</v>
       </c>
-      <c r="H121" s="25"/>
-      <c r="I121" s="6" t="s">
-        <v>550</v>
-      </c>
-      <c r="J121" s="6"/>
-    </row>
-    <row r="122" s="2" customFormat="1" spans="1:10">
+      <c r="G121" s="5"/>
+      <c r="H121" s="25" t="s">
+        <v>648</v>
+      </c>
+      <c r="I121" s="25"/>
+      <c r="J121" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="K121" s="6"/>
+    </row>
+    <row r="122" s="2" customFormat="1" spans="1:11">
       <c r="A122" s="6" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B122" s="5">
         <v>290003</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="6" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>651</v>
-      </c>
-      <c r="G122" s="25"/>
+        <v>652</v>
+      </c>
+      <c r="G122" s="5"/>
       <c r="H122" s="25"/>
-      <c r="I122" s="5"/>
-      <c r="J122" s="25"/>
-    </row>
-    <row r="123" s="2" customFormat="1" spans="1:10">
+      <c r="I122" s="25"/>
+      <c r="J122" s="5"/>
+      <c r="K122" s="25"/>
+    </row>
+    <row r="123" s="2" customFormat="1" spans="1:11">
       <c r="A123" s="6" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B123" s="5">
         <v>710014</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>656</v>
-      </c>
-      <c r="G123" s="4" t="s">
         <v>657</v>
       </c>
-      <c r="H123" s="25"/>
-      <c r="I123" s="6"/>
-      <c r="J123" s="25"/>
-    </row>
-    <row r="124" spans="1:10">
+      <c r="G123" s="5"/>
+      <c r="H123" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="I123" s="25"/>
+      <c r="J123" s="6"/>
+      <c r="K123" s="25"/>
+    </row>
+    <row r="124" spans="1:11">
       <c r="A124" s="4" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B124" s="5">
         <v>200006</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>661</v>
-      </c>
-      <c r="G124" s="4" t="s">
         <v>662</v>
       </c>
-      <c r="I124" s="6" t="s">
+      <c r="H124" s="4" t="s">
         <v>663</v>
       </c>
-      <c r="J124" s="30"/>
-    </row>
-    <row r="125" s="2" customFormat="1" spans="1:10">
+      <c r="J124" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="K124" s="30"/>
+    </row>
+    <row r="125" s="2" customFormat="1" spans="1:11">
       <c r="A125" s="6" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B125" s="5">
         <v>200010</v>
       </c>
       <c r="C125" s="6"/>
       <c r="D125" s="6" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>666</v>
-      </c>
-      <c r="G125" s="25"/>
+        <v>667</v>
+      </c>
+      <c r="G125" s="5"/>
       <c r="H125" s="25"/>
       <c r="I125" s="25"/>
       <c r="J125" s="25"/>
-    </row>
-    <row r="126" s="2" customFormat="1" spans="1:10">
+      <c r="K125" s="25"/>
+    </row>
+    <row r="126" s="2" customFormat="1" spans="1:11">
       <c r="A126" s="6" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B126" s="5">
         <v>200015</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="6" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>670</v>
-      </c>
-      <c r="G126" s="25" t="s">
         <v>671</v>
       </c>
-      <c r="H126" s="25"/>
+      <c r="G126" s="5"/>
+      <c r="H126" s="25" t="s">
+        <v>672</v>
+      </c>
       <c r="I126" s="25"/>
       <c r="J126" s="25"/>
-    </row>
-    <row r="127" s="2" customFormat="1" spans="1:11">
+      <c r="K126" s="25"/>
+    </row>
+    <row r="127" s="2" customFormat="1" spans="1:12">
       <c r="A127" s="6" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B127" s="5">
         <v>200020</v>
       </c>
       <c r="C127" s="28"/>
       <c r="D127" s="6" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>675</v>
-      </c>
-      <c r="G127" s="25" t="s">
         <v>676</v>
       </c>
-      <c r="H127" s="25"/>
-      <c r="I127" s="25" t="s">
+      <c r="G127" s="5"/>
+      <c r="H127" s="25" t="s">
         <v>677</v>
       </c>
+      <c r="I127" s="25"/>
       <c r="J127" s="25" t="s">
         <v>678</v>
       </c>
-      <c r="K127" s="31"/>
-    </row>
-    <row r="128" s="2" customFormat="1" spans="1:12">
+      <c r="K127" s="25" t="s">
+        <v>679</v>
+      </c>
+      <c r="L127" s="31"/>
+    </row>
+    <row r="128" s="2" customFormat="1" spans="1:13">
       <c r="A128" s="6" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B128" s="5">
         <v>100004</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="6" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>682</v>
-      </c>
-      <c r="G128" s="4" t="s">
         <v>683</v>
       </c>
-      <c r="H128" s="25"/>
+      <c r="G128" s="5"/>
+      <c r="H128" s="4" t="s">
+        <v>684</v>
+      </c>
       <c r="I128" s="25"/>
-      <c r="J128" s="25" t="s">
-        <v>684</v>
-      </c>
-      <c r="L128" s="31"/>
-    </row>
-    <row r="129" s="2" customFormat="1" spans="1:12">
+      <c r="J128" s="25"/>
+      <c r="K128" s="25" t="s">
+        <v>685</v>
+      </c>
+      <c r="M128" s="31"/>
+    </row>
+    <row r="129" s="2" customFormat="1" spans="1:13">
       <c r="A129" s="6" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B129" s="5">
         <v>100010</v>
       </c>
       <c r="C129" s="6"/>
       <c r="D129" s="6" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>688</v>
-      </c>
-      <c r="G129" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="H129" s="25"/>
+      <c r="G129" s="5"/>
+      <c r="H129" s="4" t="s">
+        <v>690</v>
+      </c>
       <c r="I129" s="25"/>
-      <c r="J129" s="25" t="s">
-        <v>690</v>
-      </c>
-      <c r="L129" s="31"/>
-    </row>
-    <row r="130" s="2" customFormat="1" spans="1:12">
+      <c r="J129" s="25"/>
+      <c r="K129" s="25" t="s">
+        <v>691</v>
+      </c>
+      <c r="M129" s="31"/>
+    </row>
+    <row r="130" s="2" customFormat="1" spans="1:13">
       <c r="A130" s="6" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B130" s="5">
         <v>590023</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>695</v>
-      </c>
-      <c r="G130" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="H130" s="4"/>
-      <c r="I130" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="G130" s="5"/>
+      <c r="H130" s="4" t="s">
         <v>428</v>
       </c>
+      <c r="I130" s="4"/>
       <c r="J130" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="L130" s="31"/>
-    </row>
-    <row r="131" s="2" customFormat="1" spans="1:12">
+      <c r="K130" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="M130" s="31"/>
+    </row>
+    <row r="131" s="2" customFormat="1" spans="1:13">
       <c r="A131" s="6" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B131" s="5">
         <v>590201</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>700</v>
-      </c>
-      <c r="G131" s="4" t="s">
         <v>701</v>
       </c>
-      <c r="H131" s="4"/>
-      <c r="I131" s="4" t="s">
+      <c r="G131" s="5"/>
+      <c r="H131" s="4" t="s">
         <v>702</v>
       </c>
-      <c r="J131" s="4"/>
-      <c r="K131" s="2" t="s">
+      <c r="I131" s="4"/>
+      <c r="J131" s="4" t="s">
         <v>703</v>
       </c>
-      <c r="L131" s="31"/>
-    </row>
-    <row r="132" s="2" customFormat="1" ht="17.25" spans="1:12">
+      <c r="K131" s="4"/>
+      <c r="L131" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="M131" s="31"/>
+    </row>
+    <row r="132" s="2" customFormat="1" ht="17.25" spans="1:13">
       <c r="A132" s="6" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B132" s="5">
         <v>440015</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F132" s="32"/>
-      <c r="G132" s="4"/>
+      <c r="G132" s="32"/>
       <c r="H132" s="4"/>
       <c r="I132" s="4"/>
       <c r="J132" s="4"/>
-      <c r="L132" s="31"/>
-    </row>
-    <row r="133" s="2" customFormat="1" spans="1:12">
+      <c r="K132" s="4"/>
+      <c r="M132" s="31"/>
+    </row>
+    <row r="133" s="2" customFormat="1" spans="1:13">
       <c r="A133" s="6" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B133" s="5">
         <v>450015</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F133" s="5"/>
-      <c r="G133" s="4"/>
+      <c r="G133" s="5"/>
       <c r="H133" s="4"/>
       <c r="I133" s="4"/>
       <c r="J133" s="4"/>
-      <c r="L133" s="31"/>
-    </row>
-    <row r="134" s="2" customFormat="1" spans="1:12">
+      <c r="K133" s="4"/>
+      <c r="M133" s="31"/>
+    </row>
+    <row r="134" s="2" customFormat="1" spans="1:13">
       <c r="A134" s="6" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B134" s="5">
         <v>450044</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F134" s="5"/>
-      <c r="G134" s="4"/>
+      <c r="G134" s="5"/>
       <c r="H134" s="4"/>
       <c r="I134" s="4"/>
       <c r="J134" s="4"/>
-      <c r="L134" s="31"/>
-    </row>
-    <row r="135" s="2" customFormat="1" spans="1:10">
+      <c r="K134" s="4"/>
+      <c r="M134" s="31"/>
+    </row>
+    <row r="135" s="2" customFormat="1" spans="1:11">
       <c r="A135" s="6" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B135" s="5">
         <v>490012</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>718</v>
-      </c>
-      <c r="G135" s="25"/>
+        <v>719</v>
+      </c>
+      <c r="G135" s="5"/>
       <c r="H135" s="25"/>
-      <c r="I135" s="5"/>
-      <c r="J135" s="6"/>
-    </row>
-    <row r="136" s="2" customFormat="1" spans="1:10">
+      <c r="I135" s="25"/>
+      <c r="J135" s="5"/>
+      <c r="K135" s="6"/>
+    </row>
+    <row r="136" s="2" customFormat="1" spans="1:11">
       <c r="A136" s="6" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B136" s="5">
         <v>300003</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>723</v>
-      </c>
-      <c r="G136" s="25"/>
+        <v>724</v>
+      </c>
+      <c r="G136" s="5"/>
       <c r="H136" s="25"/>
-      <c r="I136" s="5"/>
-      <c r="J136" s="6"/>
-    </row>
-    <row r="137" s="2" customFormat="1" spans="1:10">
+      <c r="I136" s="25"/>
+      <c r="J136" s="5"/>
+      <c r="K136" s="6"/>
+    </row>
+    <row r="137" s="2" customFormat="1" spans="1:11">
       <c r="A137" s="6" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B137" s="5">
         <v>330004</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E137" s="33" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
       <c r="I137" s="5"/>
-      <c r="J137" s="6"/>
-    </row>
-    <row r="138" s="2" customFormat="1" ht="15" spans="1:10">
+      <c r="J137" s="5"/>
+      <c r="K137" s="6"/>
+    </row>
+    <row r="138" s="2" customFormat="1" ht="15" spans="1:11">
       <c r="A138" s="6" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B138" s="5">
         <v>390019</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="G138" s="5"/>
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
-      <c r="J138" s="6"/>
-    </row>
-    <row r="139" s="2" customFormat="1" spans="1:10">
+      <c r="J138" s="5"/>
+      <c r="K138" s="6"/>
+    </row>
+    <row r="139" s="2" customFormat="1" spans="1:11">
       <c r="A139" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B139" s="5">
         <v>390022</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>738</v>
-      </c>
-      <c r="G139" s="25"/>
+        <v>739</v>
+      </c>
+      <c r="G139" s="5"/>
       <c r="H139" s="25"/>
-      <c r="I139" s="5"/>
-      <c r="J139" s="6"/>
-    </row>
-    <row r="140" s="2" customFormat="1" spans="1:10">
+      <c r="I139" s="25"/>
+      <c r="J139" s="5"/>
+      <c r="K139" s="6"/>
+    </row>
+    <row r="140" s="2" customFormat="1" spans="1:11">
       <c r="A140" s="6" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B140" s="5">
         <v>390023</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>743</v>
-      </c>
-      <c r="G140" s="25"/>
+        <v>744</v>
+      </c>
+      <c r="G140" s="5"/>
       <c r="H140" s="25"/>
-      <c r="I140" s="5"/>
-      <c r="J140" s="6"/>
-    </row>
-    <row r="141" s="2" customFormat="1" spans="1:12">
+      <c r="I140" s="25"/>
+      <c r="J140" s="5"/>
+      <c r="K140" s="6"/>
+    </row>
+    <row r="141" s="2" customFormat="1" spans="1:13">
       <c r="A141" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B141" s="5">
         <v>600004</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>748</v>
-      </c>
-      <c r="G141" s="4"/>
-      <c r="H141" s="25"/>
-      <c r="I141" s="25"/>
+        <v>749</v>
+      </c>
+      <c r="G141" s="25">
+        <v>20250430</v>
+      </c>
+      <c r="H141" s="4"/>
       <c r="J141" s="25"/>
-      <c r="L141" s="31"/>
+      <c r="K141" s="25"/>
+      <c r="M141" s="31"/>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="4" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B142" s="5">
         <v>600005</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="143" s="2" customFormat="1" spans="1:12">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="143" s="2" customFormat="1" spans="1:13">
       <c r="A143" s="6" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B143" s="5">
         <v>600006</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E143" s="5"/>
       <c r="F143" s="5" t="s">
-        <v>752</v>
-      </c>
-      <c r="G143" s="4"/>
-      <c r="H143" s="25"/>
+        <v>753</v>
+      </c>
+      <c r="G143" s="5"/>
+      <c r="H143" s="4"/>
       <c r="I143" s="25"/>
       <c r="J143" s="25"/>
-      <c r="L143" s="31"/>
-    </row>
-    <row r="144" s="2" customFormat="1" ht="15" spans="1:10">
+      <c r="K143" s="25"/>
+      <c r="M143" s="31"/>
+    </row>
+    <row r="144" s="2" customFormat="1" ht="15" spans="1:11">
       <c r="A144" s="6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B144" s="5">
         <v>600008</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
       <c r="G144" s="5"/>
       <c r="H144" s="5"/>
       <c r="I144" s="5"/>
-      <c r="J144" s="6"/>
-    </row>
-    <row r="145" s="2" customFormat="1" spans="1:10">
+      <c r="J144" s="5"/>
+      <c r="K144" s="6"/>
+    </row>
+    <row r="145" s="2" customFormat="1" spans="1:11">
       <c r="A145" s="6" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B145" s="5">
         <v>600009</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E145" s="5"/>
       <c r="F145" s="5"/>
-      <c r="G145" s="25"/>
+      <c r="G145" s="5"/>
       <c r="H145" s="25"/>
-      <c r="I145" s="5"/>
-      <c r="J145" s="6"/>
-    </row>
-    <row r="146" s="2" customFormat="1" spans="1:10">
+      <c r="I145" s="25"/>
+      <c r="J145" s="5"/>
+      <c r="K145" s="6"/>
+    </row>
+    <row r="146" s="2" customFormat="1" spans="1:11">
       <c r="A146" s="6" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B146" s="5">
         <v>600012</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E146" s="5"/>
       <c r="F146" s="5"/>
-      <c r="G146" s="25"/>
+      <c r="G146" s="5"/>
       <c r="H146" s="25"/>
-      <c r="I146" s="5"/>
-      <c r="J146" s="6"/>
-    </row>
-    <row r="147" s="2" customFormat="1" spans="1:10">
+      <c r="I146" s="25"/>
+      <c r="J146" s="5"/>
+      <c r="K146" s="6"/>
+    </row>
+    <row r="147" s="2" customFormat="1" spans="1:11">
       <c r="A147" s="6" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B147" s="5">
         <v>600013</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E147" s="5"/>
       <c r="F147" s="5" t="s">
-        <v>768</v>
-      </c>
-      <c r="G147" s="25"/>
+        <v>769</v>
+      </c>
+      <c r="G147" s="5"/>
       <c r="H147" s="25"/>
-      <c r="I147" s="5"/>
-      <c r="J147" s="6"/>
-    </row>
-    <row r="148" s="2" customFormat="1" ht="15" spans="1:10">
+      <c r="I147" s="25"/>
+      <c r="J147" s="5"/>
+      <c r="K147" s="6"/>
+    </row>
+    <row r="148" s="2" customFormat="1" ht="15" spans="1:11">
       <c r="A148" s="6" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B148" s="5">
         <v>600016</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="F148" s="34" t="s">
-        <v>773</v>
-      </c>
-      <c r="G148" s="5"/>
+        <v>774</v>
+      </c>
+      <c r="G148" s="34"/>
       <c r="H148" s="5"/>
       <c r="I148" s="5"/>
-      <c r="J148" s="6"/>
-    </row>
-    <row r="149" s="2" customFormat="1" spans="1:10">
+      <c r="J148" s="5"/>
+      <c r="K148" s="6"/>
+    </row>
+    <row r="149" s="2" customFormat="1" spans="1:11">
       <c r="A149" s="6" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B149" s="5">
         <v>600019</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="E149" s="5"/>
       <c r="F149" s="5"/>
-      <c r="G149" s="25"/>
+      <c r="G149" s="5"/>
       <c r="H149" s="25"/>
-      <c r="I149" s="5"/>
-      <c r="J149" s="6"/>
-    </row>
-    <row r="150" s="2" customFormat="1" spans="1:10">
+      <c r="I149" s="25"/>
+      <c r="J149" s="5"/>
+      <c r="K149" s="6"/>
+    </row>
+    <row r="150" s="2" customFormat="1" spans="1:11">
       <c r="A150" s="6" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B150" s="5">
         <v>600022</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E150" s="5"/>
       <c r="F150" s="5"/>
-      <c r="G150" s="25"/>
+      <c r="G150" s="5"/>
       <c r="H150" s="25"/>
-      <c r="I150" s="5"/>
-      <c r="J150" s="6"/>
-    </row>
-    <row r="151" s="2" customFormat="1" spans="1:10">
+      <c r="I150" s="25"/>
+      <c r="J150" s="5"/>
+      <c r="K150" s="6"/>
+    </row>
+    <row r="151" s="2" customFormat="1" spans="1:11">
       <c r="A151" s="6" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B151" s="5">
         <v>600024</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F151" s="34" t="s">
-        <v>784</v>
-      </c>
-      <c r="G151" s="4" t="s">
         <v>785</v>
       </c>
-      <c r="H151" s="25"/>
-      <c r="I151" s="5"/>
-      <c r="J151" s="6"/>
-    </row>
-    <row r="152" s="2" customFormat="1" spans="1:10">
+      <c r="G151" s="34"/>
+      <c r="H151" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="I151" s="25"/>
+      <c r="J151" s="5"/>
+      <c r="K151" s="6"/>
+    </row>
+    <row r="152" s="2" customFormat="1" spans="1:11">
       <c r="A152" s="6" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B152" s="5">
         <v>600026</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="E152" s="5"/>
       <c r="F152" s="5"/>
-      <c r="G152" s="25"/>
+      <c r="G152" s="5"/>
       <c r="H152" s="25"/>
-      <c r="I152" s="5"/>
-      <c r="J152" s="6"/>
-    </row>
-    <row r="153" s="2" customFormat="1" spans="1:10">
+      <c r="I152" s="25"/>
+      <c r="J152" s="5"/>
+      <c r="K152" s="6"/>
+    </row>
+    <row r="153" s="2" customFormat="1" spans="1:11">
       <c r="A153" s="6" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B153" s="5">
         <v>600027</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="E153" s="5"/>
       <c r="F153" s="5"/>
-      <c r="G153" s="25"/>
+      <c r="G153" s="5"/>
       <c r="H153" s="25"/>
-      <c r="I153" s="5"/>
-      <c r="J153" s="6"/>
-    </row>
-    <row r="154" s="2" customFormat="1" spans="1:10">
+      <c r="I153" s="25"/>
+      <c r="J153" s="5"/>
+      <c r="K153" s="6"/>
+    </row>
+    <row r="154" s="2" customFormat="1" spans="1:11">
       <c r="A154" s="6" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B154" s="5">
         <v>600028</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E154" s="5"/>
       <c r="F154" s="5"/>
-      <c r="G154" s="25"/>
+      <c r="G154" s="5"/>
       <c r="H154" s="25"/>
-      <c r="I154" s="5"/>
-      <c r="J154" s="6"/>
-    </row>
-    <row r="155" s="2" customFormat="1" spans="1:10">
+      <c r="I154" s="25"/>
+      <c r="J154" s="5"/>
+      <c r="K154" s="6"/>
+    </row>
+    <row r="155" s="2" customFormat="1" spans="1:11">
       <c r="A155" s="6"/>
       <c r="B155" s="5"/>
       <c r="C155" s="6"/>
       <c r="D155" s="6"/>
       <c r="E155" s="5"/>
       <c r="F155" s="5"/>
-      <c r="G155" s="25"/>
+      <c r="G155" s="5"/>
       <c r="H155" s="25"/>
-      <c r="I155" s="5"/>
-      <c r="J155" s="6"/>
-    </row>
-    <row r="156" customFormat="1" ht="17.25" spans="1:10">
+      <c r="I155" s="25"/>
+      <c r="J155" s="5"/>
+      <c r="K155" s="6"/>
+    </row>
+    <row r="156" customFormat="1" ht="17.25" spans="1:11">
       <c r="A156" s="35"/>
       <c r="B156" s="5" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="6"/>
       <c r="E156" s="5"/>
       <c r="F156" s="32"/>
-      <c r="G156" s="4"/>
+      <c r="G156" s="32"/>
       <c r="H156" s="4"/>
       <c r="I156" s="4"/>
       <c r="J156" s="4"/>
-    </row>
-    <row r="157" customFormat="1" spans="1:10">
+      <c r="K156" s="4"/>
+    </row>
+    <row r="157" customFormat="1" spans="1:11">
       <c r="A157" s="35"/>
       <c r="B157" s="5" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C157" s="6"/>
       <c r="D157" s="6"/>
       <c r="E157" s="5"/>
       <c r="F157" s="5"/>
-      <c r="G157" s="4"/>
+      <c r="G157" s="5"/>
       <c r="H157" s="4"/>
       <c r="I157" s="4"/>
       <c r="J157" s="4"/>
-    </row>
-    <row r="158" customFormat="1" spans="1:10">
+      <c r="K157" s="4"/>
+    </row>
+    <row r="158" customFormat="1" spans="1:11">
       <c r="A158" s="6"/>
       <c r="B158" s="5"/>
       <c r="C158" s="6"/>
       <c r="D158" s="6"/>
       <c r="E158" s="5"/>
       <c r="F158" s="5"/>
-      <c r="G158" s="4"/>
+      <c r="G158" s="5"/>
       <c r="H158" s="4"/>
       <c r="I158" s="4"/>
       <c r="J158" s="4"/>
-    </row>
-    <row r="159" spans="6:6">
+      <c r="K158" s="4"/>
+    </row>
+    <row r="159" spans="6:7">
       <c r="F159" s="36"/>
+      <c r="G159" s="36"/>
     </row>
     <row r="161" ht="17.25" spans="4:4">
       <c r="D161" s="32"/>

--- a/其它文件/报告模板登记.xlsx
+++ b/其它文件/报告模板登记.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19035" windowHeight="12105"/>
+    <workbookView windowWidth="20550" windowHeight="11475"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2836,31 +2836,31 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="55">
+  <fonts count="56">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2976,7 +2976,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2989,7 +2989,7 @@
     <font>
       <i/>
       <sz val="12"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -3023,6 +3023,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9.8"/>
       <color rgb="FF067D17"/>
       <name val="Courier New"/>
@@ -3045,7 +3051,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -3053,14 +3059,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -3068,7 +3074,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -3076,7 +3082,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -3084,7 +3090,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -3092,7 +3098,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -3100,14 +3106,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -3115,7 +3121,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -3123,7 +3129,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -3131,14 +3137,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -3146,42 +3152,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -3531,139 +3537,139 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3775,60 +3781,63 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="51">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
     <cellStyle name="常规_Sheet1" xfId="49"/>
     <cellStyle name="常规_Sheet1_14" xfId="50"/>
   </cellStyles>
@@ -4092,18 +4101,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O163"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="40.247619047619" style="4" customWidth="1"/>
-    <col min="2" max="2" width="14.247619047619" style="5" customWidth="1"/>
-    <col min="3" max="3" width="15.5047619047619" style="6" customWidth="1"/>
+    <col min="1" max="1" width="40.25" style="4" customWidth="1"/>
+    <col min="2" max="2" width="14.25" style="5" customWidth="1"/>
+    <col min="3" max="3" width="15.5083333333333" style="6" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" customWidth="1"/>
     <col min="5" max="5" width="13" style="5" customWidth="1"/>
-    <col min="6" max="7" width="27.3714285714286" style="5" customWidth="1"/>
-    <col min="8" max="8" width="13.8571428571429" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.752380952381" style="4" customWidth="1"/>
-    <col min="10" max="10" width="19.7142857142857" style="4" customWidth="1"/>
-    <col min="11" max="11" width="28.3714285714286" style="4" customWidth="1"/>
+    <col min="6" max="7" width="27.375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="13.8583333333333" style="4" customWidth="1"/>
+    <col min="9" max="9" width="13.75" style="4" customWidth="1"/>
+    <col min="10" max="10" width="19.7166666666667" style="4" customWidth="1"/>
+    <col min="11" max="11" width="28.375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -4514,7 +4523,7 @@
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" ht="15.75" spans="1:10">
       <c r="A22" s="4" t="s">
         <v>96</v>
       </c>
@@ -4578,7 +4587,7 @@
       <c r="J24" s="4"/>
       <c r="K24" s="21"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" ht="15.75" spans="1:8">
       <c r="A25" s="9" t="s">
         <v>106</v>
       </c>
@@ -5110,7 +5119,7 @@
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
     </row>
-    <row r="47" customFormat="1" spans="1:12">
+    <row r="47" customFormat="1" ht="15.75" spans="1:12">
       <c r="A47" s="9" t="s">
         <v>216</v>
       </c>
@@ -5279,7 +5288,7 @@
       </c>
       <c r="K52" s="4"/>
     </row>
-    <row r="53" customFormat="1" spans="1:15">
+    <row r="53" customFormat="1" ht="15.75" spans="1:15">
       <c r="A53" s="6" t="s">
         <v>254</v>
       </c>
@@ -5314,7 +5323,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="54" customFormat="1" spans="1:12">
+    <row r="54" customFormat="1" ht="15.75" spans="1:12">
       <c r="A54" s="6" t="s">
         <v>263</v>
       </c>
@@ -5348,7 +5357,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="55" customFormat="1" spans="1:11">
+    <row r="55" customFormat="1" ht="15.75" spans="1:11">
       <c r="A55" s="6" t="s">
         <v>272</v>
       </c>
@@ -6008,7 +6017,7 @@
       </c>
       <c r="K79" s="4"/>
     </row>
-    <row r="80" customFormat="1" spans="1:15">
+    <row r="80" customFormat="1" ht="15.75" spans="1:15">
       <c r="A80" s="5" t="s">
         <v>412</v>
       </c>
@@ -6108,7 +6117,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="83" s="2" customFormat="1" spans="1:11">
+    <row r="83" s="2" customFormat="1" ht="15.75" spans="1:11">
       <c r="A83" s="19" t="s">
         <v>438</v>
       </c>
@@ -7034,7 +7043,7 @@
       <c r="J117" s="25"/>
       <c r="K117" s="5"/>
     </row>
-    <row r="118" s="2" customFormat="1" spans="1:11">
+    <row r="118" s="2" customFormat="1" ht="15.75" spans="1:11">
       <c r="A118" s="6" t="s">
         <v>632</v>
       </c>
@@ -7182,7 +7191,7 @@
       <c r="J123" s="6"/>
       <c r="K123" s="25"/>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" ht="15.75" spans="1:11">
       <c r="A124" s="4" t="s">
         <v>659</v>
       </c>
@@ -7329,7 +7338,9 @@
       <c r="F129" s="5" t="s">
         <v>689</v>
       </c>
-      <c r="G129" s="5"/>
+      <c r="G129" s="5">
+        <v>20250616</v>
+      </c>
       <c r="H129" s="4" t="s">
         <v>690</v>
       </c>
@@ -7527,7 +7538,7 @@
       <c r="J136" s="5"/>
       <c r="K136" s="6"/>
     </row>
-    <row r="137" s="2" customFormat="1" spans="1:11">
+    <row r="137" s="2" customFormat="1" ht="15.75" spans="1:11">
       <c r="A137" s="6" t="s">
         <v>725</v>
       </c>
@@ -7552,7 +7563,7 @@
       <c r="J137" s="5"/>
       <c r="K137" s="6"/>
     </row>
-    <row r="138" s="2" customFormat="1" ht="15" spans="1:11">
+    <row r="138" s="2" customFormat="1" spans="1:11">
       <c r="A138" s="6" t="s">
         <v>730</v>
       </c>
@@ -7643,7 +7654,7 @@
       <c r="E141" s="5" t="s">
         <v>748</v>
       </c>
-      <c r="F141" s="5" t="s">
+      <c r="F141" s="34" t="s">
         <v>749</v>
       </c>
       <c r="G141" s="25">
@@ -7695,7 +7706,7 @@
       <c r="K143" s="25"/>
       <c r="M143" s="31"/>
     </row>
-    <row r="144" s="2" customFormat="1" ht="15" spans="1:11">
+    <row r="144" s="2" customFormat="1" spans="1:11">
       <c r="A144" s="6" t="s">
         <v>757</v>
       </c>
@@ -7781,7 +7792,7 @@
       <c r="J147" s="5"/>
       <c r="K147" s="6"/>
     </row>
-    <row r="148" s="2" customFormat="1" ht="15" spans="1:11">
+    <row r="148" s="2" customFormat="1" spans="1:11">
       <c r="A148" s="6" t="s">
         <v>770</v>
       </c>
@@ -7797,10 +7808,10 @@
       <c r="E148" s="5" t="s">
         <v>773</v>
       </c>
-      <c r="F148" s="34" t="s">
+      <c r="F148" s="35" t="s">
         <v>774</v>
       </c>
-      <c r="G148" s="34"/>
+      <c r="G148" s="35"/>
       <c r="H148" s="5"/>
       <c r="I148" s="5"/>
       <c r="J148" s="5"/>
@@ -7864,10 +7875,10 @@
       <c r="E151" s="5" t="s">
         <v>784</v>
       </c>
-      <c r="F151" s="34" t="s">
+      <c r="F151" s="35" t="s">
         <v>785</v>
       </c>
-      <c r="G151" s="34"/>
+      <c r="G151" s="35"/>
       <c r="H151" s="4" t="s">
         <v>786</v>
       </c>
@@ -7952,7 +7963,7 @@
       <c r="K155" s="6"/>
     </row>
     <row r="156" customFormat="1" ht="17.25" spans="1:11">
-      <c r="A156" s="35"/>
+      <c r="A156" s="36"/>
       <c r="B156" s="5" t="s">
         <v>796</v>
       </c>
@@ -7966,8 +7977,8 @@
       <c r="J156" s="4"/>
       <c r="K156" s="4"/>
     </row>
-    <row r="157" customFormat="1" spans="1:11">
-      <c r="A157" s="35"/>
+    <row r="157" customFormat="1" ht="15.75" spans="1:11">
+      <c r="A157" s="36"/>
       <c r="B157" s="5" t="s">
         <v>797</v>
       </c>
@@ -7995,14 +8006,14 @@
       <c r="K158" s="4"/>
     </row>
     <row r="159" spans="6:7">
-      <c r="F159" s="36"/>
-      <c r="G159" s="36"/>
+      <c r="F159" s="37"/>
+      <c r="G159" s="37"/>
     </row>
     <row r="161" ht="17.25" spans="4:4">
       <c r="D161" s="32"/>
     </row>
     <row r="163" spans="3:3">
-      <c r="C163" s="37"/>
+      <c r="C163" s="38"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/其它文件/报告模板登记.xlsx
+++ b/其它文件/报告模板登记.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20550" windowHeight="11475"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3192,14 +3192,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF008000"/>
+      <sz val="10"/>
       <name val="Courier New"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF008000"/>
       <name val="Courier New"/>
       <charset val="134"/>
     </font>
@@ -4108,7 +4108,8 @@
     <col min="3" max="3" width="15.5083333333333" style="6" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" customWidth="1"/>
     <col min="5" max="5" width="13" style="5" customWidth="1"/>
-    <col min="6" max="7" width="27.375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="23.375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.625" style="5" customWidth="1"/>
     <col min="8" max="8" width="13.8583333333333" style="4" customWidth="1"/>
     <col min="9" max="9" width="13.75" style="4" customWidth="1"/>
     <col min="10" max="10" width="19.7166666666667" style="4" customWidth="1"/>
@@ -4538,6 +4539,9 @@
       </c>
       <c r="F22" s="5" t="s">
         <v>99</v>
+      </c>
+      <c r="G22" s="5">
+        <v>20250627</v>
       </c>
       <c r="J22" s="20"/>
     </row>

--- a/其它文件/报告模板登记.xlsx
+++ b/其它文件/报告模板登记.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="21210" windowHeight="10530"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
